--- a/script/data/list.xlsx
+++ b/script/data/list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishel\Desktop\python-learn\pythonProject1\githubmeidi\当日库存情况\量化需求\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishel\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04CA63B5-B1ED-4D8B-8807-3415AAE6962B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703A93C6-CB28-477C-BFF0-8C7416E4DD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="885" yWindow="2325" windowWidth="26340" windowHeight="18360" xr2:uid="{B3F25FD5-23CB-4961-973D-5F7EFE73029E}"/>
+    <workbookView xWindow="17115" yWindow="2640" windowWidth="31125" windowHeight="17190" xr2:uid="{B3F25FD5-23CB-4961-973D-5F7EFE73029E}"/>
   </bookViews>
   <sheets>
     <sheet name="2503" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="169">
   <si>
     <t>编号</t>
   </si>
@@ -156,9 +156,6 @@
     <t>0539</t>
   </si>
   <si>
-    <t>0955</t>
-  </si>
-  <si>
     <t>1175</t>
   </si>
   <si>
@@ -169,9 +166,6 @@
   </si>
   <si>
     <t>1797</t>
-  </si>
-  <si>
-    <t>1816</t>
   </si>
   <si>
     <t>2995</t>
@@ -967,10 +961,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1000/年</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>新品.上量</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -979,18 +969,23 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>新品.上量.保6月前</t>
-  </si>
-  <si>
-    <t>新品.上量.保6月前</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>周2025-03-14</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>李圆3月重庆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0955</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1816</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3375</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1139,7 +1134,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1184,6 +1179,9 @@
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1520,7 +1518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B64B7257-7777-44DA-82FC-2A7918955D58}">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.125" style="1"/>
@@ -1536,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>47</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -1601,10 +1599,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D8" s="11"/>
     </row>
@@ -1613,10 +1611,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D9" s="11"/>
     </row>
@@ -1625,10 +1623,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D10" s="11"/>
     </row>
@@ -1655,7 +1653,7 @@
         <v>1000</v>
       </c>
       <c r="D12" s="11">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -1669,7 +1667,7 @@
         <v>5000</v>
       </c>
       <c r="D13" s="11">
-        <v>20000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -1677,10 +1675,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D14" s="11"/>
     </row>
@@ -1711,7 +1709,7 @@
         <v>2000</v>
       </c>
       <c r="D17" s="11">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -1721,7 +1719,9 @@
       <c r="B18" s="11">
         <v>500</v>
       </c>
-      <c r="C18" s="11"/>
+      <c r="C18" s="11">
+        <v>500</v>
+      </c>
       <c r="D18" s="11">
         <v>1000</v>
       </c>
@@ -1731,13 +1731,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D19" s="11">
-        <v>4000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -1745,10 +1745,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D20" s="11"/>
     </row>
@@ -1771,7 +1771,7 @@
         <v>5000</v>
       </c>
       <c r="D22" s="11">
-        <v>30000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -1817,7 +1817,7 @@
         <v>5000</v>
       </c>
       <c r="D27" s="11">
-        <v>10000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -1831,7 +1831,7 @@
         <v>5000</v>
       </c>
       <c r="D28" s="11">
-        <v>8000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -1846,14 +1846,14 @@
       <c r="A30" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>164</v>
+      <c r="B30" s="14">
+        <v>500</v>
+      </c>
+      <c r="C30" s="14">
+        <v>500</v>
       </c>
       <c r="D30" s="11">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -1867,7 +1867,7 @@
         <v>5000</v>
       </c>
       <c r="D31" s="11">
-        <v>10000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -1907,12 +1907,12 @@
         <v>1500</v>
       </c>
       <c r="D34" s="11">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="12" t="s">
-        <v>34</v>
+      <c r="A35" s="12">
+        <v>5891</v>
       </c>
       <c r="B35" s="11">
         <v>1000</v>
@@ -1920,29 +1920,41 @@
       <c r="C35" s="11">
         <v>1000</v>
       </c>
-      <c r="D35" s="11"/>
+      <c r="D35" s="11">
+        <v>5000</v>
+      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
+        <v>34</v>
+      </c>
+      <c r="B36" s="11">
+        <v>1000</v>
+      </c>
+      <c r="C36" s="11">
+        <v>1000</v>
+      </c>
       <c r="D36" s="11">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
+        <v>35</v>
+      </c>
+      <c r="B37" s="11">
+        <v>1000</v>
+      </c>
+      <c r="C37" s="11">
+        <v>1000</v>
+      </c>
+      <c r="D37" s="11">
+        <v>3000</v>
+      </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -1950,67 +1962,61 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="11">
-        <v>2000</v>
-      </c>
-      <c r="C39" s="11">
-        <v>2000</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
       <c r="D39" s="11"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="11">
+        <v>2000</v>
+      </c>
+      <c r="C40" s="11">
+        <v>2000</v>
+      </c>
+      <c r="D40" s="11">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="15" t="s">
         <v>166</v>
-      </c>
-      <c r="D40" s="11"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="12" t="s">
-        <v>40</v>
       </c>
       <c r="B41" s="11"/>
       <c r="C41" s="11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D41" s="11"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="11">
-        <v>500</v>
-      </c>
-      <c r="C42" s="11">
-        <v>500</v>
-      </c>
-      <c r="D42" s="11">
-        <v>1000</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D42" s="11"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B43" s="11">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="C43" s="11">
-        <v>2000</v>
-      </c>
-      <c r="D43" s="11">
-        <v>2000</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="D43" s="11"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B44" s="11">
         <v>1000</v>
@@ -2019,34 +2025,66 @@
         <v>1000</v>
       </c>
       <c r="D44" s="11">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="11">
+        <v>1000</v>
+      </c>
+      <c r="C45" s="11">
+        <v>1000</v>
+      </c>
+      <c r="D45" s="11">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B46" s="11">
+        <v>1000</v>
+      </c>
+      <c r="C46" s="11">
+        <v>1000</v>
+      </c>
+      <c r="D46" s="11">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="D45" s="11"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="D46" s="11"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="13"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
+      <c r="D47" s="11">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="11">
+        <v>500</v>
+      </c>
+      <c r="C48" s="11">
+        <v>500</v>
+      </c>
+      <c r="D48" s="11">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="13"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2066,160 +2104,160 @@
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H15">
         <v>4588</v>
@@ -2227,30 +2265,30 @@
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H16">
         <v>515</v>
       </c>
       <c r="J16" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="H17">
         <v>273</v>
@@ -2258,13 +2296,13 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="H18">
         <v>4328</v>
@@ -2272,13 +2310,13 @@
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H19">
         <v>4791</v>
@@ -2286,38 +2324,38 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
@@ -2329,37 +2367,37 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C26" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
@@ -2371,18 +2409,18 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
       <c r="I27" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
@@ -2391,127 +2429,127 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B31" s="2"/>
       <c r="C31" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H35" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I35" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B36" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
@@ -2523,119 +2561,119 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H41" s="8">
         <v>1796</v>
       </c>
       <c r="I41" s="8"/>
       <c r="J41" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K41" s="8"/>
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="H42">
         <v>1797</v>
       </c>
       <c r="J42" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H43">
         <v>1755</v>
       </c>
       <c r="J43" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H46">
         <v>5855</v>
       </c>
       <c r="J46" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K46" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
